--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92568285268</v>
+        <v>46157.93097722562</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93097722562</v>
+        <v>46157.93172884743</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93172884743</v>
+        <v>46157.93400086405</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93400086405</v>
+        <v>46157.93717978616</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93717978616</v>
+        <v>46158.28216321173</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28216321173</v>
+        <v>46158.29681476942</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29681476942</v>
+        <v>46158.29814678733</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29814678733</v>
+        <v>46158.33387408234</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33387408234</v>
+        <v>46158.36857147918</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36857147918</v>
+        <v>46158.3728783592</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
